--- a/ch_06_regression_models/ch_06_solution.xlsx
+++ b/ch_06_regression_models/ch_06_solution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_06_regression_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC891AC0-18F0-44C5-AC5C-CB1FD18A835C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091BFD9B-0513-4B1A-A6E6-D802C1E58039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="9">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -84,41 +84,13 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="10"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="11"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="9">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -133,18 +105,6 @@
     </bk>
     <bk>
       <rc t="2" v="4"/>
-    </bk>
-    <bk>
-      <rc t="2" v="5"/>
-    </bk>
-    <bk>
-      <rc t="2" v="6"/>
-    </bk>
-    <bk>
-      <rc t="2" v="7"/>
-    </bk>
-    <bk>
-      <rc t="2" v="8"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -242,6 +202,16 @@
 logit_results_df["odds_ratio"]</code>
     </pythonScript>
     <pythonScript>
+      <code xml:space="preserve"># Get predicted probabilities 
+penguins_df["prob_gentoo"] = logit_model.predict(X) 
+# Convert probabilities to predictions (&gt; 0.5 = Gentoo) 
+penguins_df["predicted_gentoo"] = (penguins_df["prob_gentoo"] &gt; 0.5).astype(int) 
+# Check accuracy 
+correct = (penguins_df["predicted_gentoo"] == penguins_df["is_gentoo"]).sum() 
+total = len(penguins_df) 
+f"Correct: {correct} out of {total}, Accuracy: {round(correct / total * 100, 1)}%%" </code>
+    </pythonScript>
+    <pythonScript>
       <code># Shuffle the data and split: 80%% training, 20%% testing
 df_shuffled = penguins_df.sample(frac=1, random_state=42)
 split_point = int(len(df_shuffled) * 0.8)
@@ -295,7 +265,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="16">
   <si>
     <t>species</t>
   </si>
@@ -344,14 +314,14 @@
   <si>
     <t/>
   </si>
-  <si>
-    <t>TRAIN TEST SPLIT</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -381,9 +351,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,7 +383,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>521390</xdr:colOff>
+      <xdr:colOff>89590</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>135466</xdr:rowOff>
     </xdr:to>
@@ -456,13 +427,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>736600</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>148166</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>292100</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>11727</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -478,7 +449,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="regression!A80"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="regression!A81"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -648,7 +619,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="12">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
   <rv s="0">
     <fb>0</fb>
     <v>2</v>
@@ -677,47 +648,15 @@
     <v>Image generated by Python</v>
   </rv>
   <rv s="5">
-    <fb t="s">Predicted flipper length: 205.1 mm</fb>
-    <v>&lt;class 'str'&gt;</v>
-    <v>str</v>
-    <v>Predicted flipper length: 205.1 mm</v>
-    <v>Predicted flipper length: 205.1 mm</v>
+    <v>&lt;class 'statsmodels.regression.linear_model.RegressionResultsWrapper'&gt;</v>
+    <v>RegressionResultsWrapper</v>
+    <v>&lt;statsmodels.regression.linear_model.RegressionResultsWrapper object at 0x7f1fdcc4d9d0&gt;</v>
     <v>3</v>
   </rv>
   <rv s="5">
-    <fb t="s">Training set: 273 rows, Test set: 69 rows</fb>
-    <v>&lt;class 'str'&gt;</v>
-    <v>str</v>
-    <v>Training set: 273 rows, Test set: 69 rows</v>
-    <v>Training set: 273 rows, Test set: 69 rows</v>
-    <v>3</v>
-  </rv>
-  <rv s="6">
-    <v>&lt;class 'statsmodels.regression.linear_model.RegressionResultsWrapper'&gt;</v>
-    <v>RegressionResultsWrapper</v>
-    <v>&lt;statsmodels.regression.linear_model.RegressionResultsWrapper object at 0x7f60fc96cbc0&gt;</v>
-    <v>3</v>
-  </rv>
-  <rv s="5">
-    <fb t="s">Mean Absolute Error on test set: 4.44 mm</fb>
-    <v>&lt;class 'str'&gt;</v>
-    <v>str</v>
-    <v>Mean Absolute Error on test set: 4.44 mm</v>
-    <v>Mean Absolute Error on test set: 4.44 mm</v>
-    <v>3</v>
-  </rv>
-  <rv s="6">
     <v>&lt;class 'statsmodels.discrete.discrete_model.BinaryResultsWrapper'&gt;</v>
     <v>BinaryResultsWrapper</v>
-    <v>&lt;statsmodels.discrete.discrete_model.BinaryResultsWrapper object at 0x7f61026c2d50&gt;</v>
-    <v>3</v>
-  </rv>
-  <rv s="5">
-    <fb t="s">Test set accuracy: 100.0%, Correct: 69 out of 69</fb>
-    <v>&lt;class 'str'&gt;</v>
-    <v>str</v>
-    <v>Test set accuracy: 100.0%, Correct: 69 out of 69</v>
-    <v>Test set accuracy: 100.0%, Correct: 69 out of 69</v>
+    <v>&lt;statsmodels.discrete.discrete_model.BinaryResultsWrapper object at 0x7f1fdcb35d60&gt;</v>
     <v>3</v>
   </rv>
   <rv s="4">
@@ -729,7 +668,7 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <s t="_formattednumber">
     <k n="_Format" t="spb"/>
   </s>
@@ -752,13 +691,6 @@
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
     <k n="CalcOrigin" t="i"/>
     <k n="Text" t="s"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="basicValue" t="s"/>
-    <k n="_Provider" t="spb"/>
   </s>
   <s t="_python">
     <k n="Python_type" t="s"/>
@@ -9079,10 +9011,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC4F1B38-9D94-4787-80D6-7F7A9A81E059}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="19.87890625" customWidth="1"/>
+    <col min="1" max="1" width="45.64453125" customWidth="1"/>
+    <col min="2" max="2" width="14.9375" customWidth="1"/>
     <col min="3" max="3" width="11.76171875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.3515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -9387,27 +9320,35 @@
         <v>1.6194165952385566E-2</v>
       </c>
     </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+    </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A36" t="str" cm="1">
         <f t="array" ref="A36:G40">_xlfn._xlws.PY(5,0)</f>
         <v/>
       </c>
-      <c r="B36" t="str">
+      <c r="B36" s="2" t="str">
         <v>Coef.</v>
       </c>
-      <c r="C36" t="str">
+      <c r="C36" s="2" t="str">
         <v>Std.Err.</v>
       </c>
-      <c r="D36" t="str">
+      <c r="D36" s="2" t="str">
         <v>t</v>
       </c>
-      <c r="E36" t="str">
+      <c r="E36" s="2" t="str">
         <v>P&gt;|t|</v>
       </c>
-      <c r="F36" t="str">
+      <c r="F36" s="2" t="str">
         <v>[0.025</v>
       </c>
-      <c r="G36" t="str">
+      <c r="G36" s="2" t="str">
         <v>0.975]</v>
       </c>
     </row>
@@ -9415,22 +9356,22 @@
       <c r="A37" t="str">
         <v>const</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="2">
         <v>157.78594228892464</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="2">
         <v>4.62612702376566</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>34.107568053867908</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="2">
         <v>1.798098946270445E-111</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2">
         <v>148.68631661310306</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="2">
         <v>166.88556796474623</v>
       </c>
     </row>
@@ -9438,22 +9379,22 @@
       <c r="A38" t="str">
         <v>body_mass_g</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="2">
         <v>1.0925613623574675E-2</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="2">
         <v>5.3838729154386032E-4</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>20.293223475325306</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="2">
         <v>1.9316462647763306E-60</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2">
         <v>9.866601885137655E-3</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="2">
         <v>1.1984625362011695E-2</v>
       </c>
     </row>
@@ -9461,22 +9402,22 @@
       <c r="A39" t="str">
         <v>bill_length_mm</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="2">
         <v>0.59227310410359102</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="2">
         <v>7.1733108603349013E-2</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>8.2566211842092052</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="2">
         <v>3.4163878761004644E-15</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2">
         <v>0.45117355506392814</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="2">
         <v>0.73337265314325384</v>
       </c>
     </row>
@@ -9484,28 +9425,28 @@
       <c r="A40" t="str">
         <v>bill_depth_mm</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="2">
         <v>-1.6786762054930051</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="2">
         <v>0.1807708351612041</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>-9.2862114842586738</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="2">
         <v>1.9947988739516662E-18</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="2">
         <v>-2.0342537598104866</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="2">
         <v>-1.3230986511755236</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A43" t="str" cm="1" vm="3">
-        <f t="array" ref="A43">_xlfn._xlws.PY(6,1)</f>
+      <c r="A43" t="str" cm="1">
+        <f t="array" ref="A43">_xlfn._xlws.PY(6,0)</f>
         <v>Predicted flipper length: 205.1 mm</v>
       </c>
     </row>
@@ -9539,22 +9480,22 @@
         <f t="array" ref="A51:G53">_xlfn._xlws.PY(8,0)</f>
         <v/>
       </c>
-      <c r="B51" t="str">
+      <c r="B51" s="2" t="str">
         <v>Coef.</v>
       </c>
-      <c r="C51" t="str">
+      <c r="C51" s="2" t="str">
         <v>Std.Err.</v>
       </c>
-      <c r="D51" t="str">
+      <c r="D51" s="2" t="str">
         <v>z</v>
       </c>
-      <c r="E51" t="str">
+      <c r="E51" s="2" t="str">
         <v>P&gt;|z|</v>
       </c>
-      <c r="F51" t="str">
+      <c r="F51" s="2" t="str">
         <v>[0.025</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G51" s="2" t="str">
         <v>0.975]</v>
       </c>
     </row>
@@ -9562,22 +9503,22 @@
       <c r="A52" t="str">
         <v>const</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="2">
         <v>-28.418060420068237</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="2">
         <v>3.6096409011787181</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="2">
         <v>-7.8728220335680481</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="2">
         <v>3.4672971353533646E-15</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="2">
         <v>-35.492826583501227</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="2">
         <v>-21.343294256635247</v>
       </c>
     </row>
@@ -9585,22 +9526,22 @@
       <c r="A53" t="str">
         <v>body_mass_g</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="2">
         <v>6.3708851978764086E-3</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="2">
         <v>8.1316878295239765E-4</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <v>7.834640644646286</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="2">
         <v>4.7018550221959556E-15</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="2">
         <v>4.777103669937441E-3</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="2">
         <v>7.964666725815377E-3</v>
       </c>
     </row>
@@ -9617,7 +9558,7 @@
       <c r="A57" t="str">
         <v>const</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="2">
         <v>4.5519048279169813E-13</v>
       </c>
     </row>
@@ -9625,48 +9566,49 @@
       <c r="A58" t="str">
         <v>body_mass_g</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="2">
         <v>1.0063912224528118</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A61" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A63" t="str" cm="1" vm="4">
-        <f t="array" ref="A63">_xlfn._xlws.PY(10,1)</f>
+      <c r="A61" t="str" cm="1">
+        <f t="array" ref="A61">_xlfn._xlws.PY(10,0)</f>
+        <v>Correct: 314 out of 342, Accuracy: 91.8%</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A64" t="str" cm="1">
+        <f t="array" ref="A64">_xlfn._xlws.PY(11,0)</f>
         <v>Training set: 273 rows, Test set: 69 rows</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A67" t="e" cm="1" vm="5">
-        <f t="array" ref="A67">_xlfn._xlws.PY(11,1)</f>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A68" t="e" cm="1" vm="3">
+        <f t="array" ref="A68">_xlfn._xlws.PY(12,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A70" t="str" cm="1" vm="6">
-        <f t="array" ref="A70">_xlfn._xlws.PY(12,1)</f>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A71" t="str" cm="1">
+        <f t="array" ref="A71">_xlfn._xlws.PY(13,0)</f>
         <v>Mean Absolute Error on test set: 4.44 mm</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A73" t="e" cm="1" vm="7">
-        <f t="array" ref="A73">_xlfn._xlws.PY(13,1)</f>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A74" t="e" cm="1" vm="4">
+        <f t="array" ref="A74">_xlfn._xlws.PY(14,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A76" t="str" cm="1" vm="8">
-        <f t="array" ref="A76">_xlfn._xlws.PY(14,1)</f>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A77" t="str" cm="1">
+        <f t="array" ref="A77">_xlfn._xlws.PY(15,0)</f>
         <v>Test set accuracy: 100.0%, Correct: 69 out of 69</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A80" t="e" cm="1" vm="9">
-        <f t="array" ref="A80">_xlfn._xlws.PY(15,0)</f>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A81" t="e" cm="1" vm="5">
+        <f t="array" ref="A81">_xlfn._xlws.PY(16,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/ch_06_regression_models/ch_06_solution.xlsx
+++ b/ch_06_regression_models/ch_06_solution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30021"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_06_regression_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091BFD9B-0513-4B1A-A6E6-D802C1E58039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972CF25A-C510-419A-B5CD-2C5F3524AE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="6">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -84,13 +84,20 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="6">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -105,6 +112,9 @@
     </bk>
     <bk>
       <rc t="2" v="4"/>
+    </bk>
+    <bk>
+      <rc t="2" v="5"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -169,15 +179,15 @@
 results_multi_df</code>
     </pythonScript>
     <pythonScript>
-      <code># Predict flipper length for a hypothetical penguin
-new_penguin = pd.DataFrame({
-    "const": [1],
-    "body_mass_g": [4200],
-    "bill_length_mm": [45],
-    "bill_depth_mm": [15]
-})
-predicted = model_multi.predict(new_penguin)
-"Predicted flipper length: " + str(round(predicted[0], 1)) + " mm"</code>
+      <code xml:space="preserve"># Predict flipper length for a hypothetical penguin 
+new_penguin = pd.DataFrame({ 
+     "const": [1], 
+     "body_mass_g": [4200], 
+     "bill_length_mm": [45], 
+     "bill_depth_mm": [15] 
+}) 
+predicted = model_multi.predict(new_penguin) 
+f"Predicted flipper length: {round(predicted[0], 1)} mm" </code>
     </pythonScript>
     <pythonScript>
       <code># Create a binary outcome: 1 if Gentoo, 0 otherwise
@@ -185,16 +195,14 @@
 penguins_df["is_gentoo"].value_counts()</code>
     </pythonScript>
     <pythonScript>
-      <code># Use a simpler, stable set of predictors
-X = penguins_df[["body_mass_g"]]  # keep it to one variable
-y = penguins_df["is_gentoo"]
-# Add constant
-X = sm.add_constant(X)
-# Fit model (no regularization)
-logit_model = sm.Logit(y, X).fit()
-# Tidy results table
-logit_results_df = logit_model.summary2().tables[1]
-logit_results_df</code>
+      <code xml:space="preserve">X_logit = penguins_df[["body_mass_g"]]  
+y_logit = penguins_df["is_gentoo"] 
+# Add constant 
+X_logit = sm.add_constant(X_logit) 
+# Fit model  
+logit_model = sm.Logit(y_logit, X_logit).fit() 
+# Tidy results table 
+logit_results_df = logit_model.summary2().tables[1] </code>
     </pythonScript>
     <pythonScript>
       <code># Add odds ratios
@@ -203,7 +211,7 @@
     </pythonScript>
     <pythonScript>
       <code xml:space="preserve"># Get predicted probabilities 
-penguins_df["prob_gentoo"] = logit_model.predict(X) 
+penguins_df["prob_gentoo"] = logit_model.predict(X_logit) 
 # Convert probabilities to predictions (&gt; 0.5 = Gentoo) 
 penguins_df["predicted_gentoo"] = (penguins_df["prob_gentoo"] &gt; 0.5).astype(int) 
 # Check accuracy 
@@ -212,12 +220,12 @@
 f"Correct: {correct} out of {total}, Accuracy: {round(correct / total * 100, 1)}%%" </code>
     </pythonScript>
     <pythonScript>
-      <code># Shuffle the data and split: 80%% training, 20%% testing
-df_shuffled = penguins_df.sample(frac=1, random_state=42)
-split_point = int(len(df_shuffled) * 0.8)
-train = df_shuffled.iloc[:split_point]
-test = df_shuffled.iloc[split_point:]
-"Training set: " + str(len(train)) + " rows, Test set: " + str(len(test)) + " rows"</code>
+      <code xml:space="preserve"># Shuffle the data and split: 80%% training, 20%% testing 
+df_shuffled = penguins_df.sample(frac=1, random_state=42) 
+split_point = int(len(df_shuffled) * 0.8) 
+train = df_shuffled.iloc[:split_point] 
+test = df_shuffled.iloc[split_point:] 
+print(f"Training set: {len(train)} rows, Test set: {len(test)} rows") </code>
     </pythonScript>
     <pythonScript>
       <code># Fit on training data only
@@ -619,7 +627,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <fb>0</fb>
     <v>2</v>
@@ -647,16 +655,20 @@
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
+  <rv s="0">
+    <fb>0</fb>
+    <v>4</v>
+  </rv>
   <rv s="5">
     <v>&lt;class 'statsmodels.regression.linear_model.RegressionResultsWrapper'&gt;</v>
     <v>RegressionResultsWrapper</v>
-    <v>&lt;statsmodels.regression.linear_model.RegressionResultsWrapper object at 0x7f1fdcc4d9d0&gt;</v>
+    <v>&lt;statsmodels.regression.linear_model.RegressionResultsWrapper object at 0x7f9e3bd6a7b0&gt;</v>
     <v>3</v>
   </rv>
   <rv s="5">
     <v>&lt;class 'statsmodels.discrete.discrete_model.BinaryResultsWrapper'&gt;</v>
     <v>BinaryResultsWrapper</v>
-    <v>&lt;statsmodels.discrete.discrete_model.BinaryResultsWrapper object at 0x7f1fdcb35d60&gt;</v>
+    <v>&lt;statsmodels.discrete.discrete_model.BinaryResultsWrapper object at 0x7f9e4744a780&gt;</v>
     <v>3</v>
   </rv>
   <rv s="4">
@@ -703,7 +715,7 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="4">
+  <spbData count="5">
     <spb s="0">
       <v>344</v>
       <v>7</v>
@@ -721,6 +733,9 @@
       <v>https://www.anaconda.com/excel</v>
       <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
       <v>Python provided by Anaconda</v>
+    </spb>
+    <spb s="2">
+      <v>2</v>
     </spb>
   </spbData>
 </supportingPropertyBags>
@@ -762,6 +777,9 @@
   <richStyles>
     <rSty dxfid="0">
       <rpv i="0">0;-0;"nan"</rpv>
+    </rSty>
+    <rSty dxfid="0">
+      <rpv i="0">0;-0;"None"</rpv>
     </rSty>
   </richStyles>
 </richStyleSheet>
@@ -9577,13 +9595,13 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A64" t="str" cm="1">
+      <c r="A64" cm="1" vm="3">
         <f t="array" ref="A64">_xlfn._xlws.PY(11,0)</f>
-        <v>Training set: 273 rows, Test set: 69 rows</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A68" t="e" cm="1" vm="3">
+      <c r="A68" t="e" cm="1" vm="4">
         <f t="array" ref="A68">_xlfn._xlws.PY(12,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -9595,7 +9613,7 @@
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A74" t="e" cm="1" vm="4">
+      <c r="A74" t="e" cm="1" vm="5">
         <f t="array" ref="A74">_xlfn._xlws.PY(14,1)</f>
         <v>#VALUE!</v>
       </c>
@@ -9607,7 +9625,7 @@
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A81" t="e" cm="1" vm="5">
+      <c r="A81" t="e" cm="1" vm="6">
         <f t="array" ref="A81">_xlfn._xlws.PY(16,0)</f>
         <v>#VALUE!</v>
       </c>

--- a/ch_06_regression_models/ch_06_solution.xlsx
+++ b/ch_06_regression_models/ch_06_solution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30021"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30112"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_06_regression_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972CF25A-C510-419A-B5CD-2C5F3524AE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAF74B1-CA92-447B-9719-5EC6484BBDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,6 +170,10 @@
 results_df</code>
     </pythonScript>
     <pythonScript>
+      <code># Fit the model
+results_df_2 = model.summary2().tables[0]</code>
+    </pythonScript>
+    <pythonScript>
       <code># Multiple predictors
 X_multi = penguins_df[["body_mass_g", "bill_length_mm", "bill_depth_mm"]]
 y = penguins_df["flipper_length_mm"]
@@ -177,6 +181,9 @@
 model_multi = sm.OLS(y, X_multi).fit()
 results_multi_df = model_multi.summary2().tables[1]
 results_multi_df</code>
+    </pythonScript>
+    <pythonScript>
+      <code>results_multi_df_2 = model_multi.summary2().tables[0]</code>
     </pythonScript>
     <pythonScript>
       <code xml:space="preserve"># Predict flipper length for a hypothetical penguin 
@@ -390,8 +397,8 @@
       <xdr:rowOff>101599</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>89590</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>948956</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>135466</xdr:rowOff>
     </xdr:to>
@@ -435,13 +442,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>736600</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>148166</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>11727</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -457,7 +464,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="regression!A81"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="regression!A101"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -662,13 +669,13 @@
   <rv s="5">
     <v>&lt;class 'statsmodels.regression.linear_model.RegressionResultsWrapper'&gt;</v>
     <v>RegressionResultsWrapper</v>
-    <v>&lt;statsmodels.regression.linear_model.RegressionResultsWrapper object at 0x7f9e3bd6a7b0&gt;</v>
+    <v>&lt;statsmodels.regression.linear_model.RegressionResultsWrapper object at 0x7f30509be930&gt;</v>
     <v>3</v>
   </rv>
   <rv s="5">
     <v>&lt;class 'statsmodels.discrete.discrete_model.BinaryResultsWrapper'&gt;</v>
     <v>BinaryResultsWrapper</v>
-    <v>&lt;statsmodels.discrete.discrete_model.BinaryResultsWrapper object at 0x7f9e4744a780&gt;</v>
+    <v>&lt;statsmodels.discrete.discrete_model.BinaryResultsWrapper object at 0x7f304551e780&gt;</v>
     <v>3</v>
   </rv>
   <rv s="4">
@@ -9029,12 +9036,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC4F1B38-9D94-4787-80D6-7F7A9A81E059}">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="45.64453125" customWidth="1"/>
-    <col min="2" max="2" width="14.9375" customWidth="1"/>
-    <col min="3" max="3" width="11.76171875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.3515625" customWidth="1"/>
+    <col min="3" max="3" width="14.29296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5859375" customWidth="1"/>
     <col min="7" max="7" width="12.3515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9339,294 +9347,501 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A36" t="str" cm="1">
-        <f t="array" ref="A36:G40">_xlfn._xlws.PY(5,0)</f>
-        <v/>
-      </c>
-      <c r="B36" s="2" t="str">
-        <v>Coef.</v>
-      </c>
-      <c r="C36" s="2" t="str">
-        <v>Std.Err.</v>
+        <f t="array" ref="A36:D42">_xlfn._xlws.PY(5,0)</f>
+        <v>Model:</v>
+      </c>
+      <c r="B36" t="str">
+        <v>OLS</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Adj. R-squared:</v>
       </c>
       <c r="D36" s="2" t="str">
-        <v>t</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v>P&gt;|t|</v>
-      </c>
-      <c r="F36" s="2" t="str">
-        <v>[0.025</v>
-      </c>
-      <c r="G36" s="2" t="str">
-        <v>0.975]</v>
+        <v>0.758</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A37" t="str">
-        <v>const</v>
-      </c>
-      <c r="B37" s="2">
-        <v>157.78594228892464</v>
-      </c>
-      <c r="C37" s="2">
-        <v>4.62612702376566</v>
-      </c>
-      <c r="D37" s="2">
-        <v>34.107568053867908</v>
-      </c>
-      <c r="E37" s="2">
-        <v>1.798098946270445E-111</v>
-      </c>
-      <c r="F37" s="2">
-        <v>148.68631661310306</v>
-      </c>
-      <c r="G37" s="2">
-        <v>166.88556796474623</v>
+        <v>Dependent Variable:</v>
+      </c>
+      <c r="B37" t="str">
+        <v>flipper_length_mm</v>
+      </c>
+      <c r="C37" t="str">
+        <v>AIC:</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <v>2295.0351</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A38" t="str">
-        <v>body_mass_g</v>
-      </c>
-      <c r="B38" s="2">
-        <v>1.0925613623574675E-2</v>
-      </c>
-      <c r="C38" s="2">
-        <v>5.3838729154386032E-4</v>
-      </c>
-      <c r="D38" s="2">
-        <v>20.293223475325306</v>
-      </c>
-      <c r="E38" s="2">
-        <v>1.9316462647763306E-60</v>
-      </c>
-      <c r="F38" s="2">
-        <v>9.866601885137655E-3</v>
-      </c>
-      <c r="G38" s="2">
-        <v>1.1984625362011695E-2</v>
+        <v>Date:</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-05-16 19:12</v>
+      </c>
+      <c r="C38" t="str">
+        <v>BIC:</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <v>2302.7047</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A39" t="str">
-        <v>bill_length_mm</v>
-      </c>
-      <c r="B39" s="2">
-        <v>0.59227310410359102</v>
-      </c>
-      <c r="C39" s="2">
-        <v>7.1733108603349013E-2</v>
-      </c>
-      <c r="D39" s="2">
-        <v>8.2566211842092052</v>
-      </c>
-      <c r="E39" s="2">
-        <v>3.4163878761004644E-15</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0.45117355506392814</v>
-      </c>
-      <c r="G39" s="2">
-        <v>0.73337265314325384</v>
+        <v>No. Observations:</v>
+      </c>
+      <c r="B39" t="str">
+        <v>342</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Log-Likelihood:</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <v>-1145.5</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A40" t="str">
+        <v>Df Model:</v>
+      </c>
+      <c r="B40" t="str">
+        <v>1</v>
+      </c>
+      <c r="C40" t="str">
+        <v>F-statistic:</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <v>1071.</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A41" t="str">
+        <v>Df Residuals:</v>
+      </c>
+      <c r="B41" t="str">
+        <v>340</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Prob (F-statistic):</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <v>4.37e-107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A42" t="str">
+        <v>R-squared:</v>
+      </c>
+      <c r="B42" t="str">
+        <v>0.759</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Scale:</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <v>47.795</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A45" t="str" cm="1">
+        <f t="array" ref="A45:G49">_xlfn._xlws.PY(6,0)</f>
+        <v/>
+      </c>
+      <c r="B45" s="2" t="str">
+        <v>Coef.</v>
+      </c>
+      <c r="C45" s="2" t="str">
+        <v>Std.Err.</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <v>t</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <v>P&gt;|t|</v>
+      </c>
+      <c r="F45" s="2" t="str">
+        <v>[0.025</v>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>0.975]</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A46" t="str">
+        <v>const</v>
+      </c>
+      <c r="B46" s="2">
+        <v>157.78594228892464</v>
+      </c>
+      <c r="C46" s="2">
+        <v>4.62612702376566</v>
+      </c>
+      <c r="D46" s="2">
+        <v>34.107568053867908</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1.798098946270445E-111</v>
+      </c>
+      <c r="F46" s="2">
+        <v>148.68631661310306</v>
+      </c>
+      <c r="G46" s="2">
+        <v>166.88556796474623</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A47" t="str">
+        <v>body_mass_g</v>
+      </c>
+      <c r="B47" s="2">
+        <v>1.0925613623574675E-2</v>
+      </c>
+      <c r="C47" s="2">
+        <v>5.3838729154386032E-4</v>
+      </c>
+      <c r="D47" s="2">
+        <v>20.293223475325306</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1.9316462647763306E-60</v>
+      </c>
+      <c r="F47" s="2">
+        <v>9.866601885137655E-3</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1.1984625362011695E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A48" t="str">
+        <v>bill_length_mm</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.59227310410359102</v>
+      </c>
+      <c r="C48" s="2">
+        <v>7.1733108603349013E-2</v>
+      </c>
+      <c r="D48" s="2">
+        <v>8.2566211842092052</v>
+      </c>
+      <c r="E48" s="2">
+        <v>3.4163878761004644E-15</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.45117355506392814</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0.73337265314325384</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A49" t="str">
         <v>bill_depth_mm</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B49" s="2">
         <v>-1.6786762054930051</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C49" s="2">
         <v>0.1807708351612041</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D49" s="2">
         <v>-9.2862114842586738</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E49" s="2">
         <v>1.9947988739516662E-18</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F49" s="2">
         <v>-2.0342537598104866</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G49" s="2">
         <v>-1.3230986511755236</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A43" t="str" cm="1">
-        <f t="array" ref="A43">_xlfn._xlws.PY(6,0)</f>
-        <v>Predicted flipper length: 205.1 mm</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A46" t="str" cm="1">
-        <f t="array" ref="A46:B48">_xlfn._xlws.PY(7,0)</f>
-        <v>is_gentoo</v>
-      </c>
-      <c r="B46" t="str">
-        <v>count</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A47">
-        <v>0</v>
-      </c>
-      <c r="B47">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A48">
-        <v>1</v>
-      </c>
-      <c r="B48">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A51" t="str" cm="1">
-        <f t="array" ref="A51:G53">_xlfn._xlws.PY(8,0)</f>
-        <v/>
-      </c>
-      <c r="B51" s="2" t="str">
-        <v>Coef.</v>
-      </c>
-      <c r="C51" s="2" t="str">
-        <v>Std.Err.</v>
-      </c>
-      <c r="D51" s="2" t="str">
-        <v>z</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v>P&gt;|z|</v>
-      </c>
-      <c r="F51" s="2" t="str">
-        <v>[0.025</v>
-      </c>
-      <c r="G51" s="2" t="str">
-        <v>0.975]</v>
-      </c>
-    </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A52" t="str">
-        <v>const</v>
-      </c>
-      <c r="B52" s="2">
-        <v>-28.418060420068237</v>
-      </c>
-      <c r="C52" s="2">
-        <v>3.6096409011787181</v>
-      </c>
-      <c r="D52" s="2">
-        <v>-7.8728220335680481</v>
-      </c>
-      <c r="E52" s="2">
-        <v>3.4672971353533646E-15</v>
-      </c>
-      <c r="F52" s="2">
-        <v>-35.492826583501227</v>
-      </c>
-      <c r="G52" s="2">
-        <v>-21.343294256635247</v>
+      <c r="A52" t="str" cm="1">
+        <f t="array" ref="A52:D58">_xlfn._xlws.PY(7,0)</f>
+        <v>Model:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>OLS</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Adj. R-squared:</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <v>0.830</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A53" t="str">
-        <v>body_mass_g</v>
-      </c>
-      <c r="B53" s="2">
-        <v>6.3708851978764086E-3</v>
-      </c>
-      <c r="C53" s="2">
-        <v>8.1316878295239765E-4</v>
-      </c>
-      <c r="D53" s="2">
-        <v>7.834640644646286</v>
-      </c>
-      <c r="E53" s="2">
-        <v>4.7018550221959556E-15</v>
-      </c>
-      <c r="F53" s="2">
-        <v>4.777103669937441E-3</v>
-      </c>
-      <c r="G53" s="2">
-        <v>7.964666725815377E-3</v>
+        <v>Dependent Variable:</v>
+      </c>
+      <c r="B53" t="str">
+        <v>flipper_length_mm</v>
+      </c>
+      <c r="C53" t="str">
+        <v>AIC:</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <v>2176.8792</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A54" t="str">
+        <v>Date:</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-05-16 19:12</v>
+      </c>
+      <c r="C54" t="str">
+        <v>BIC:</v>
+      </c>
+      <c r="D54" s="1" t="str">
+        <v>2192.2184</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A55" t="str">
+        <v>No. Observations:</v>
+      </c>
+      <c r="B55" t="str">
+        <v>342</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Log-Likelihood:</v>
+      </c>
+      <c r="D55" s="1" t="str">
+        <v>-1084.4</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A56" t="str" cm="1">
-        <f t="array" ref="A56:B58">_xlfn._xlws.PY(9,0)</f>
-        <v/>
+      <c r="A56" t="str">
+        <v>Df Model:</v>
       </c>
       <c r="B56" t="str">
-        <v>odds_ratio</v>
+        <v>3</v>
+      </c>
+      <c r="C56" t="str">
+        <v>F-statistic:</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <v>555.5</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A57" t="str">
-        <v>const</v>
-      </c>
-      <c r="B57" s="2">
-        <v>4.5519048279169813E-13</v>
+        <v>Df Residuals:</v>
+      </c>
+      <c r="B57" t="str">
+        <v>338</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Prob (F-statistic):</v>
+      </c>
+      <c r="D57" s="1" t="str">
+        <v>2.99e-130</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A58" t="str">
+        <v>R-squared:</v>
+      </c>
+      <c r="B58" t="str">
+        <v>0.831</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Scale:</v>
+      </c>
+      <c r="D58" s="1" t="str">
+        <v>33.637</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="D60" s="1"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A63" t="str" cm="1">
+        <f t="array" ref="A63">_xlfn._xlws.PY(8,0)</f>
+        <v>Predicted flipper length: 205.1 mm</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A66" t="str" cm="1">
+        <f t="array" ref="A66:B68">_xlfn._xlws.PY(9,0)</f>
+        <v>is_gentoo</v>
+      </c>
+      <c r="B66" t="str">
+        <v>count</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A67">
+        <v>0</v>
+      </c>
+      <c r="B67">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A68">
+        <v>1</v>
+      </c>
+      <c r="B68">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A71" t="str" cm="1">
+        <f t="array" ref="A71:G73">_xlfn._xlws.PY(10,0)</f>
+        <v/>
+      </c>
+      <c r="B71" s="2" t="str">
+        <v>Coef.</v>
+      </c>
+      <c r="C71" s="2" t="str">
+        <v>Std.Err.</v>
+      </c>
+      <c r="D71" s="2" t="str">
+        <v>z</v>
+      </c>
+      <c r="E71" s="2" t="str">
+        <v>P&gt;|z|</v>
+      </c>
+      <c r="F71" s="2" t="str">
+        <v>[0.025</v>
+      </c>
+      <c r="G71" s="2" t="str">
+        <v>0.975]</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A72" t="str">
+        <v>const</v>
+      </c>
+      <c r="B72" s="2">
+        <v>-28.418060420068237</v>
+      </c>
+      <c r="C72" s="2">
+        <v>3.6096409011787181</v>
+      </c>
+      <c r="D72" s="2">
+        <v>-7.8728220335680481</v>
+      </c>
+      <c r="E72" s="2">
+        <v>3.4672971353533646E-15</v>
+      </c>
+      <c r="F72" s="2">
+        <v>-35.492826583501227</v>
+      </c>
+      <c r="G72" s="2">
+        <v>-21.343294256635247</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A73" t="str">
         <v>body_mass_g</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B73" s="2">
+        <v>6.3708851978764086E-3</v>
+      </c>
+      <c r="C73" s="2">
+        <v>8.1316878295239765E-4</v>
+      </c>
+      <c r="D73" s="2">
+        <v>7.834640644646286</v>
+      </c>
+      <c r="E73" s="2">
+        <v>4.7018550221959556E-15</v>
+      </c>
+      <c r="F73" s="2">
+        <v>4.777103669937441E-3</v>
+      </c>
+      <c r="G73" s="2">
+        <v>7.964666725815377E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A76" t="str" cm="1">
+        <f t="array" ref="A76:B78">_xlfn._xlws.PY(11,0)</f>
+        <v/>
+      </c>
+      <c r="B76" t="str">
+        <v>odds_ratio</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A77" t="str">
+        <v>const</v>
+      </c>
+      <c r="B77" s="2">
+        <v>4.5519048279169813E-13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
+      <c r="A78" t="str">
+        <v>body_mass_g</v>
+      </c>
+      <c r="B78" s="2">
         <v>1.0063912224528118</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A61" t="str" cm="1">
-        <f t="array" ref="A61">_xlfn._xlws.PY(10,0)</f>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A81" t="str" cm="1">
+        <f t="array" ref="A81">_xlfn._xlws.PY(12,0)</f>
         <v>Correct: 314 out of 342, Accuracy: 91.8%</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A64" cm="1" vm="3">
-        <f t="array" ref="A64">_xlfn._xlws.PY(11,0)</f>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A84" cm="1" vm="3">
+        <f t="array" ref="A84">_xlfn._xlws.PY(13,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A68" t="e" cm="1" vm="4">
-        <f t="array" ref="A68">_xlfn._xlws.PY(12,1)</f>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A88" t="e" cm="1" vm="4">
+        <f t="array" ref="A88">_xlfn._xlws.PY(14,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A71" t="str" cm="1">
-        <f t="array" ref="A71">_xlfn._xlws.PY(13,0)</f>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A91" t="str" cm="1">
+        <f t="array" ref="A91">_xlfn._xlws.PY(15,0)</f>
         <v>Mean Absolute Error on test set: 4.44 mm</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A74" t="e" cm="1" vm="5">
-        <f t="array" ref="A74">_xlfn._xlws.PY(14,1)</f>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A94" t="e" cm="1" vm="5">
+        <f t="array" ref="A94">_xlfn._xlws.PY(16,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A77" t="str" cm="1">
-        <f t="array" ref="A77">_xlfn._xlws.PY(15,0)</f>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A97" t="str" cm="1">
+        <f t="array" ref="A97">_xlfn._xlws.PY(17,0)</f>
         <v>Test set accuracy: 100.0%, Correct: 69 out of 69</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.5">
-      <c r="A81" t="e" cm="1" vm="6">
-        <f t="array" ref="A81">_xlfn._xlws.PY(16,0)</f>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A101" t="e" cm="1" vm="6">
+        <f t="array" ref="A101">_xlfn._xlws.PY(18,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
